--- a/HumanEval/CD Authors.xlsx
+++ b/HumanEval/CD Authors.xlsx
@@ -4,7 +4,8 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="rudra.dhar@research.iiit.ac.in" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="adyanshkakran@gmail.com" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="rudra.dhar@research.iiit.ac.in" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,15 +13,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="54">
   <si>
     <t>Timestamp</t>
+  </si>
+  <si>
+    <t>Name</t>
   </si>
   <si>
     <t>User</t>
   </si>
   <si>
     <t>ADR_ID</t>
+  </si>
+  <si>
+    <t>Decision_ID</t>
   </si>
   <si>
     <t>Model_A</t>
@@ -71,10 +78,7 @@
     <t>Model_D_Comment</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Decision_ID</t>
+    <t>Adyansh Kakran</t>
   </si>
   <si>
     <t>Rudra Dhar</t>
@@ -83,16 +87,22 @@
     <t>DRAFT</t>
   </si>
   <si>
+    <t>Finetuning</t>
+  </si>
+  <si>
     <t>The ground truth Decision seems incomplete.</t>
+  </si>
+  <si>
+    <t>RAFG</t>
   </si>
   <si>
     <t>Prompting</t>
   </si>
   <si>
-    <t>Finetuning</t>
+    <t>insanely long decision for a simple ADR entry</t>
   </si>
   <si>
-    <t>RAFG</t>
+    <t>too long</t>
   </si>
   <si>
     <t>Generation incomplete.</t>
@@ -107,10 +117,64 @@
     <t>Generation didn't complete.</t>
   </si>
   <si>
+    <t>matched the final output of the ground truth, but the decision is very incomplete</t>
+  </si>
+  <si>
+    <t>hallucinated</t>
+  </si>
+  <si>
+    <t>too long for such a simple decision</t>
+  </si>
+  <si>
+    <t>javascript is chosen a lot by LLMs</t>
+  </si>
+  <si>
+    <t>what is python for back end (should be some framework)</t>
+  </si>
+  <si>
+    <t>what is java for backend</t>
+  </si>
+  <si>
+    <t>very similar to another decision</t>
+  </si>
+  <si>
     <t>Needlessly repeating the context.</t>
   </si>
   <si>
     <t>Don't need to blabber so much detail.</t>
+  </si>
+  <si>
+    <t>wow conflicts with itself</t>
+  </si>
+  <si>
+    <t>Hallucinating !</t>
+  </si>
+  <si>
+    <t>Hallucinating.</t>
+  </si>
+  <si>
+    <t>Incomplete</t>
+  </si>
+  <si>
+    <t>Generation incomplete</t>
+  </si>
+  <si>
+    <t>The ground truth Decision is not written properly, might be an parsing issue during data collection.</t>
+  </si>
+  <si>
+    <t>The ground truth decision is itself incoherent.</t>
+  </si>
+  <si>
+    <t>Ground truth has some parsing or rendering error.</t>
+  </si>
+  <si>
+    <t>Ground truth has some parsing or rendering error. And generation seems incomplete</t>
+  </si>
+  <si>
+    <t>The ground truth has a parsing or rendering problem.</t>
+  </si>
+  <si>
+    <t>such a long decision</t>
   </si>
 </sst>
 </file>
@@ -182,6 +246,10 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -395,58 +463,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -466,58 +534,3176 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2">
+        <v>46222.91920296296</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="4">
+        <v>3849.0</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J2" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N2" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R2" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>46222.92016342592</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1353.0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N3" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R3" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>46222.93313049768</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="4">
+        <v>3382.0</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J4" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N4" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R4" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>46222.94064002315</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="4">
+        <v>4223.0</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N5" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R5" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>46222.97627422454</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="4">
+        <v>3846.0</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J6" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N6" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R6" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>46222.978440520834</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="4">
+        <v>51.0</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J7" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N7" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R7" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <v>46222.98126664352</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1684.0</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <v>46222.98441685185</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2896.0</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N9" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R9" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <v>46222.98669712963</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="4">
+        <v>250.0</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N10" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R10" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
+        <v>46222.988435590276</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="4">
+        <v>2875.0</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J11" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N11" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R11" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <v>46222.99023913195</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="4">
+        <v>3325.0</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N12" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R12" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2">
+        <v>46222.99170863426</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1610.0</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J13" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2">
+        <v>46222.99240430555</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="4">
+        <v>844.0</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2">
+        <v>46222.99424881944</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="4">
+        <v>3013.0</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2">
+        <v>46222.996479849535</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="4">
+        <v>3159.0</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J16" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N16" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R16" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2">
+        <v>46222.9978056713</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="4">
+        <v>740.0</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J17" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M17" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N17" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R17" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2">
+        <v>46222.99833752315</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="4">
+        <v>3596.0</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J18" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N18" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R18" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2">
+        <v>46222.998924375</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2804.0</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J19" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N19" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R19" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2">
+        <v>46223.00444751157</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="4">
+        <v>3231.0</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I20" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M20" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2">
+        <v>46223.00593265046</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="4">
+        <v>121.0</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F21" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M21" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N21" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R21" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2">
+        <v>46223.00708084491</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="4">
+        <v>3247.0</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M22" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2">
+        <v>46223.00821357639</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="4">
+        <v>3926.0</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F23" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M23" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N23" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R23" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2">
+        <v>46223.00974667824</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="4">
+        <v>1069.0</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M24" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2">
+        <v>46223.01168177083</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="4">
+        <v>560.0</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F25" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I25" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J25" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M25" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2">
+        <v>46223.01407693287</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="4">
+        <v>3056.0</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F26" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J26" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M26" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N26" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R26" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2">
+        <v>46223.03685657408</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="4">
+        <v>3341.0</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F27" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J27" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M27" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N27" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R27" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2">
+        <v>46223.03737586805</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="4">
+        <v>3508.0</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F28" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J28" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M28" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <v>46223.03798137732</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="4">
+        <v>1952.0</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I29" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2">
+        <v>46223.038815312495</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="4">
+        <v>429.0</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F30" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J30" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M30" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2">
+        <v>46223.03934584491</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="4">
+        <v>501.0</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F31" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I31" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J31" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M31" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2">
+        <v>46223.04045210648</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="4">
+        <v>1275.0</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M32" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2">
+        <v>46223.04129782408</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" s="4">
+        <v>4168.0</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F33" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I33" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J33" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M33" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N33" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R33" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2">
+        <v>46223.041898993055</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" s="4">
+        <v>1482.0</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F34" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I34" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J34" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M34" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2">
+        <v>46223.04355636574</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1876.0</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F35" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I35" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J35" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M35" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N35" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R35" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2">
+        <v>46223.04418077546</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" s="4">
+        <v>1213.0</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F36" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J36" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M36" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N36" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R36" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2">
+        <v>46223.04529155092</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C37" s="4">
+        <v>2016.0</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F37" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I37" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J37" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M37" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N37" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q37" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R37" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2">
+        <v>46223.04600322917</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="4">
+        <v>3379.0</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F38" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I38" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J38" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M38" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N38" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R38" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2">
+        <v>46223.04646194444</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" s="4">
+        <v>3397.0</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F39" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I39" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J39" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M39" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N39" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P39" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R39" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2">
+        <v>46223.04739258102</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="4">
+        <v>1985.0</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F40" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I40" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J40" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M40" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N40" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R40" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2">
+        <v>46223.048106111106</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="4">
+        <v>949.0</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F41" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I41" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J41" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N41" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R41" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2">
+        <v>46223.048946145835</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C42" s="4">
+        <v>3284.0</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I42" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M42" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <v>46223.04929909723</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43" s="4">
+        <v>2889.0</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F43" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I43" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J43" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M43" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N43" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R43" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <v>46223.04992019676</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" s="4">
+        <v>709.0</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I44" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J44" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M44" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N44" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <v>46223.05070019676</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="4">
+        <v>3096.0</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F45" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I45" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J45" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M45" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N45" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R45" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <v>46223.05156528935</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="4">
+        <v>982.0</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F46" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I46" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J46" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M46" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N46" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R46" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <v>46223.05192236111</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="4">
+        <v>3344.0</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I47" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J47" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M47" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N47" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <v>46223.05305797454</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="4">
+        <v>1375.0</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F48" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I48" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J48" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M48" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N48" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R48" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2">
+        <v>46223.05389458333</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49" s="4">
+        <v>993.0</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E49" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F49" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I49" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M49" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N49" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <v>46223.055230729165</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" s="4">
+        <v>3812.0</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E50" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F50" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I50" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J50" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M50" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <v>46223.05709447917</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" s="4">
+        <v>1614.0</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F51" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I51" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J51" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M51" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2">
+        <v>46223.05789334491</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" s="4">
+        <v>855.0</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F52" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M52" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N52" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2">
+        <v>46223.0598521875</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" s="4">
+        <v>4234.0</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E53" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F53" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I53" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J53" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M53" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2">
+        <v>46223.06164818287</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54" s="4">
+        <v>3286.0</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F54" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I54" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J54" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M54" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N54" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R54" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2">
+        <v>46223.063391331016</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="4">
+        <v>3652.0</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E55" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F55" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I55" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J55" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M55" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N55" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q55" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R55" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2">
+        <v>46223.06427376157</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" s="4">
+        <v>3824.0</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E56" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F56" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I56" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J56" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M56" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N56" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P56" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q56" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R56" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2">
+        <v>46223.06860273148</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" s="4">
+        <v>2911.0</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F57" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I57" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J57" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M57" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N57" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R57" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2">
+        <v>46223.06919155092</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58" s="4">
+        <v>2062.0</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E58" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I58" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M58" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2">
+        <v>46223.070149004634</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C59" s="4">
+        <v>3143.0</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E59" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F59" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I59" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J59" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M59" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N59" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R59" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2">
+        <v>46223.07123350694</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C60" s="4">
+        <v>4075.0</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F60" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I60" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J60" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M60" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N60" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R60" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2">
+        <v>46223.072181655094</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C61" s="4">
+        <v>66.0</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I61" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M61" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P61" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2">
+        <v>46223.07375553241</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C62" s="4">
+        <v>2544.0</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I62" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J62" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M62" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N62" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R62" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2">
+        <v>46223.0744468287</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C63" s="4">
+        <v>3881.0</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F63" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I63" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J63" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M63" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P63" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2">
+        <v>46223.07498290509</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C64" s="4">
+        <v>986.0</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F64" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I64" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J64" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M64" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="P64" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2">
+        <v>46223.07680738426</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65" s="4">
+        <v>945.0</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E65" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F65" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I65" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J65" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M65" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2">
@@ -525,13 +3711,13 @@
         <v>46219.022099444446</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="4">
         <v>3849.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="3">
         <v>1.0</v>
@@ -540,10 +3726,10 @@
         <v>4.0</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I2" s="3">
         <v>1.0</v>
@@ -552,20 +3738,20 @@
         <v>4.0</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N2" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="N2" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="P2" s="3" t="s">
         <v>26</v>
       </c>
@@ -576,7 +3762,7 @@
         <v>4.0</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -584,7 +3770,7 @@
         <v>46219.53148888889</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="4">
         <v>1353.0</v>
@@ -599,7 +3785,7 @@
         <v>4.0</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I3" s="3">
         <v>1.0</v>
@@ -608,7 +3794,7 @@
         <v>4.0</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M3" s="3">
         <v>1.0</v>
@@ -617,7 +3803,7 @@
         <v>4.0</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q3" s="3">
         <v>2.0</v>
@@ -631,13 +3817,13 @@
         <v>46219.53497905092</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="4">
         <v>3382.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" s="3">
         <v>1.0</v>
@@ -646,7 +3832,7 @@
         <v>3.0</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I4" s="3">
         <v>2.0</v>
@@ -655,7 +3841,7 @@
         <v>4.0</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M4" s="3">
         <v>5.0</v>
@@ -678,13 +3864,13 @@
         <v>46219.53914247685</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="4">
         <v>4223.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" s="3">
         <v>2.0</v>
@@ -693,7 +3879,7 @@
         <v>4.0</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I5" s="3">
         <v>4.0</v>
@@ -711,7 +3897,7 @@
         <v>4.0</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q5" s="3">
         <v>2.0</v>
@@ -725,13 +3911,13 @@
         <v>46219.54259857639</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="4">
         <v>3846.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" s="3">
         <v>2.0</v>
@@ -740,7 +3926,7 @@
         <v>4.0</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I6" s="3">
         <v>2.0</v>
@@ -749,7 +3935,7 @@
         <v>4.0</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M6" s="3">
         <v>2.0</v>
@@ -772,13 +3958,13 @@
         <v>46219.56143890046</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="4">
         <v>51.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3">
         <v>2.0</v>
@@ -796,7 +3982,7 @@
         <v>4.0</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M7" s="3">
         <v>4.0</v>
@@ -805,7 +3991,7 @@
         <v>4.0</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q7" s="3">
         <v>3.0</v>
@@ -819,13 +4005,13 @@
         <v>46219.56788498843</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="4">
         <v>1684.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" s="3">
         <v>4.0</v>
@@ -834,7 +4020,7 @@
         <v>4.0</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I8" s="3">
         <v>1.0</v>
@@ -843,10 +4029,10 @@
         <v>1.0</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M8" s="3">
         <v>3.0</v>
@@ -869,13 +4055,13 @@
         <v>46219.57438608796</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="4">
         <v>2896.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" s="3">
         <v>1.0</v>
@@ -884,7 +4070,7 @@
         <v>4.0</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I9" s="3">
         <v>1.0</v>
@@ -893,7 +4079,7 @@
         <v>4.0</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M9" s="3">
         <v>1.0</v>
@@ -916,13 +4102,13 @@
         <v>46219.57952799769</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" s="4">
         <v>250.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E10" s="3">
         <v>5.0</v>
@@ -931,7 +4117,7 @@
         <v>5.0</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I10" s="3">
         <v>3.0</v>
@@ -940,10 +4126,10 @@
         <v>3.0</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M10" s="3">
         <v>3.0</v>
@@ -952,7 +4138,7 @@
         <v>3.0</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>26</v>
@@ -969,13 +4155,13 @@
         <v>46220.61913726851</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" s="4">
         <v>2875.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" s="3">
         <v>1.0</v>
@@ -984,7 +4170,7 @@
         <v>2.0</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3">
         <v>3.0</v>
@@ -1002,7 +4188,7 @@
         <v>4.0</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q11" s="3">
         <v>4.0</v>
@@ -1016,13 +4202,13 @@
         <v>46220.64885650463</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" s="4">
         <v>3325.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E12" s="3">
         <v>3.0</v>
@@ -1031,7 +4217,7 @@
         <v>3.0</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I12" s="3">
         <v>2.0</v>
@@ -1040,10 +4226,10 @@
         <v>4.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M12" s="3">
         <v>1.0</v>
@@ -1066,13 +4252,13 @@
         <v>46220.654534236106</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" s="4">
         <v>1610.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E13" s="3">
         <v>2.0</v>
@@ -1090,7 +4276,7 @@
         <v>4.0</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M13" s="3">
         <v>2.0</v>
@@ -1099,7 +4285,7 @@
         <v>3.0</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q13" s="3">
         <v>2.0</v>
@@ -1113,13 +4299,13 @@
         <v>46220.65966642361</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" s="4">
         <v>844.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E14" s="3">
         <v>2.0</v>
@@ -1128,7 +4314,7 @@
         <v>2.0</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I14" s="3">
         <v>4.0</v>
@@ -1146,7 +4332,7 @@
         <v>4.0</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q14" s="3">
         <v>4.0</v>
@@ -1160,13 +4346,13 @@
         <v>46220.661761944444</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="4">
         <v>3013.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E15" s="3">
         <v>3.0</v>
@@ -1175,7 +4361,7 @@
         <v>3.0</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I15" s="3">
         <v>2.0</v>
@@ -1193,7 +4379,7 @@
         <v>4.0</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q15" s="3">
         <v>3.0</v>
@@ -1207,13 +4393,13 @@
         <v>46220.67042738426</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" s="4">
         <v>3159.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E16" s="3">
         <v>2.0</v>
@@ -1231,7 +4417,7 @@
         <v>4.0</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M16" s="3">
         <v>2.0</v>
@@ -1240,7 +4426,7 @@
         <v>3.0</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q16" s="3">
         <v>2.0</v>
@@ -1254,13 +4440,13 @@
         <v>46220.67288979166</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" s="4">
         <v>740.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E17" s="3">
         <v>2.0</v>
@@ -1269,7 +4455,7 @@
         <v>4.0</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I17" s="3">
         <v>2.0</v>
@@ -1278,7 +4464,7 @@
         <v>3.0</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M17" s="3">
         <v>2.0</v>
@@ -1301,13 +4487,13 @@
         <v>46220.95566155092</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" s="4">
         <v>3596.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E18" s="3">
         <v>1.0</v>
@@ -1316,7 +4502,7 @@
         <v>5.0</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I18" s="3">
         <v>1.0</v>
@@ -1325,7 +4511,7 @@
         <v>1.0</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M18" s="3">
         <v>4.0</v>
@@ -1348,7 +4534,7 @@
         <v>46220.95886515046</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" s="4">
         <v>2804.0</v>
@@ -1363,7 +4549,7 @@
         <v>5.0</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I19" s="3">
         <v>3.0</v>
@@ -1372,7 +4558,7 @@
         <v>3.0</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M19" s="3">
         <v>3.0</v>
@@ -1381,7 +4567,7 @@
         <v>3.0</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q19" s="3">
         <v>3.0</v>
@@ -1395,13 +4581,13 @@
         <v>46220.96367949074</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20" s="4">
         <v>3231.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E20" s="3">
         <v>3.0</v>
@@ -1410,7 +4596,7 @@
         <v>5.0</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I20" s="3">
         <v>2.0</v>
@@ -1419,7 +4605,7 @@
         <v>4.0</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M20" s="3">
         <v>2.0</v>
@@ -1442,13 +4628,13 @@
         <v>46220.996560995365</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C21" s="4">
         <v>121.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E21" s="3">
         <v>2.0</v>
@@ -1457,7 +4643,7 @@
         <v>4.0</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I21" s="3">
         <v>2.0</v>
@@ -1475,7 +4661,7 @@
         <v>5.0</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q21" s="3">
         <v>2.0</v>
@@ -1489,13 +4675,13 @@
         <v>46220.998388611115</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C22" s="4">
         <v>3247.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E22" s="3">
         <v>1.0</v>
@@ -1504,7 +4690,7 @@
         <v>5.0</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I22" s="3">
         <v>1.0</v>
@@ -1522,7 +4708,7 @@
         <v>5.0</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q22" s="3">
         <v>1.0</v>
@@ -1536,13 +4722,13 @@
         <v>46221.001021874996</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C23" s="4">
         <v>3926.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E23" s="3">
         <v>3.0</v>
@@ -1560,7 +4746,7 @@
         <v>5.0</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M23" s="3">
         <v>3.0</v>
@@ -1569,7 +4755,7 @@
         <v>5.0</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q23" s="3">
         <v>2.0</v>
@@ -1583,13 +4769,13 @@
         <v>46221.006451608795</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C24" s="4">
         <v>1069.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E24" s="3">
         <v>1.0</v>
@@ -1598,7 +4784,7 @@
         <v>2.0</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I24" s="3">
         <v>1.0</v>
@@ -1607,7 +4793,7 @@
         <v>3.0</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M24" s="3">
         <v>2.0</v>
@@ -1630,13 +4816,13 @@
         <v>46221.01046549769</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C25" s="4">
         <v>560.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E25" s="3">
         <v>1.0</v>
@@ -1654,7 +4840,7 @@
         <v>3.0</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M25" s="3">
         <v>1.0</v>
@@ -1663,7 +4849,7 @@
         <v>3.0</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q25" s="3">
         <v>1.0</v>
@@ -1677,13 +4863,13 @@
         <v>46221.80194265046</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C26" s="4">
         <v>3056.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E26" s="3">
         <v>3.0</v>
@@ -1692,7 +4878,7 @@
         <v>3.0</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I26" s="3">
         <v>3.0</v>
@@ -1701,7 +4887,7 @@
         <v>3.0</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M26" s="3">
         <v>2.0</v>
@@ -1724,13 +4910,13 @@
         <v>46221.80576130787</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C27" s="4">
         <v>3341.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E27" s="3">
         <v>3.0</v>
@@ -1739,10 +4925,10 @@
         <v>3.0</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I27" s="3">
         <v>2.0</v>
@@ -1751,7 +4937,7 @@
         <v>3.0</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M27" s="3">
         <v>3.0</v>
@@ -1774,13 +4960,13 @@
         <v>46221.80895980324</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C28" s="4">
         <v>3508.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E28" s="3">
         <v>4.0</v>
@@ -1789,7 +4975,7 @@
         <v>4.0</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I28" s="3">
         <v>5.0</v>
@@ -1807,7 +4993,7 @@
         <v>4.0</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q28" s="3">
         <v>4.0</v>
@@ -1821,13 +5007,13 @@
         <v>46221.81442916667</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C29" s="4">
         <v>1952.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E29" s="3">
         <v>3.0</v>
@@ -1845,7 +5031,7 @@
         <v>5.0</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M29" s="3">
         <v>3.0</v>
@@ -1854,7 +5040,7 @@
         <v>4.0</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q29" s="3">
         <v>3.0</v>
@@ -1868,13 +5054,13 @@
         <v>46221.81638310185</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C30" s="4">
         <v>429.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E30" s="3">
         <v>4.0</v>
@@ -1883,7 +5069,7 @@
         <v>4.0</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I30" s="3">
         <v>4.0</v>
@@ -1892,7 +5078,7 @@
         <v>5.0</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M30" s="3">
         <v>4.0</v>
@@ -1915,13 +5101,13 @@
         <v>46221.82372100695</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C31" s="4">
         <v>501.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E31" s="3">
         <v>4.0</v>
@@ -1930,7 +5116,7 @@
         <v>4.0</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I31" s="3">
         <v>4.0</v>
@@ -1948,7 +5134,7 @@
         <v>4.0</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q31" s="3">
         <v>4.0</v>
@@ -1962,13 +5148,13 @@
         <v>46221.831970162035</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C32" s="4">
         <v>1275.0</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E32" s="3">
         <v>2.0</v>
@@ -1977,7 +5163,7 @@
         <v>3.0</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I32" s="3">
         <v>3.0</v>
@@ -1986,7 +5172,7 @@
         <v>3.0</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M32" s="3">
         <v>2.0</v>
@@ -2009,13 +5195,13 @@
         <v>46221.8376255787</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C33" s="4">
         <v>4168.0</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E33" s="3">
         <v>4.0</v>
@@ -2024,7 +5210,7 @@
         <v>4.0</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I33" s="3">
         <v>4.0</v>
@@ -2033,7 +5219,7 @@
         <v>3.0</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>26</v>
@@ -2045,10 +5231,10 @@
         <v>3.0</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q33" s="3">
         <v>4.0</v>
@@ -2062,13 +5248,13 @@
         <v>46221.856363009254</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C34" s="4">
         <v>1482.0</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E34" s="3">
         <v>3.0</v>
@@ -2077,7 +5263,7 @@
         <v>5.0</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I34" s="3">
         <v>4.0</v>
@@ -2086,7 +5272,7 @@
         <v>4.0</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M34" s="3">
         <v>4.0</v>
@@ -2109,13 +5295,13 @@
         <v>46221.879360023144</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C35" s="4">
         <v>1876.0</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E35" s="3">
         <v>2.0</v>
@@ -2124,7 +5310,7 @@
         <v>4.0</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I35" s="3">
         <v>1.0</v>
@@ -2142,7 +5328,7 @@
         <v>3.0</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q35" s="3">
         <v>2.0</v>
@@ -2156,13 +5342,13 @@
         <v>46222.04369576389</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C36" s="4">
         <v>1213.0</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E36" s="3">
         <v>1.0</v>
@@ -2180,7 +5366,7 @@
         <v>3.0</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M36" s="3">
         <v>1.0</v>
@@ -2189,7 +5375,7 @@
         <v>3.0</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q36" s="3">
         <v>1.0</v>
@@ -2203,7 +5389,7 @@
         <v>46222.04991270833</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C37" s="4">
         <v>2016.0</v>
@@ -2218,7 +5404,7 @@
         <v>3.0</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I37" s="3">
         <v>2.0</v>
@@ -2227,7 +5413,7 @@
         <v>3.0</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M37" s="3">
         <v>1.0</v>
@@ -2236,7 +5422,7 @@
         <v>3.0</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q37" s="3">
         <v>2.0</v>
@@ -2250,13 +5436,13 @@
         <v>46222.0521336574</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C38" s="4">
         <v>3379.0</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E38" s="3">
         <v>4.0</v>
@@ -2265,7 +5451,7 @@
         <v>5.0</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I38" s="3">
         <v>3.0</v>
@@ -2274,10 +5460,10 @@
         <v>4.0</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M38" s="3">
         <v>5.0</v>
@@ -2300,13 +5486,13 @@
         <v>46222.05723024305</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C39" s="4">
         <v>3397.0</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E39" s="3">
         <v>3.0</v>
@@ -2324,7 +5510,7 @@
         <v>4.0</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M39" s="3">
         <v>3.0</v>
@@ -2333,7 +5519,7 @@
         <v>5.0</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q39" s="3">
         <v>3.0</v>
@@ -2347,7 +5533,7 @@
         <v>46222.077205023146</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="4">
         <v>1985.0</v>
@@ -2362,7 +5548,7 @@
         <v>4.0</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I40" s="3">
         <v>1.0</v>
@@ -2371,7 +5557,7 @@
         <v>3.0</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M40" s="3">
         <v>2.0</v>
@@ -2380,7 +5566,7 @@
         <v>3.0</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q40" s="3">
         <v>4.0</v>
@@ -2394,7 +5580,7 @@
         <v>46222.083222974536</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C41" s="4">
         <v>949.0</v>
@@ -2409,7 +5595,7 @@
         <v>2.0</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I41" s="3">
         <v>3.0</v>
@@ -2418,21 +5604,1209 @@
         <v>4.0</v>
       </c>
       <c r="L41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M41" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N41" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R41" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2">
+        <v>46225.84744357639</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M41" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="N41" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="R41" s="3">
+      <c r="C42" s="4">
+        <v>3284.0</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I42" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M42" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <v>46225.8483959375</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="4">
+        <v>2889.0</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F43" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I43" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J43" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M43" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N43" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R43" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <v>46225.851511354165</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" s="4">
+        <v>709.0</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J44" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M44" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N44" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <v>46225.85312741898</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" s="4">
+        <v>3096.0</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F45" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I45" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J45" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M45" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N45" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R45" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <v>46225.8621784375</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="4">
+        <v>982.0</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F46" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I46" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J46" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M46" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N46" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R46" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <v>46225.86793491898</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="4">
+        <v>3344.0</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I47" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J47" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M47" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N47" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <v>46225.86991496528</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" s="4">
+        <v>1375.0</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F48" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I48" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J48" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M48" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N48" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R48" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2">
+        <v>46225.87273166666</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" s="4">
+        <v>993.0</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F49" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I49" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M49" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N49" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <v>46225.876110763886</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" s="4">
+        <v>3812.0</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E50" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F50" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I50" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J50" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M50" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="S50" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <v>46225.879093634256</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" s="4">
+        <v>1614.0</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E51" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F51" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I51" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J51" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M51" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2">
+        <v>46225.88399270833</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52" s="4">
+        <v>855.0</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F52" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M52" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N52" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2">
+        <v>46225.88633916667</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C53" s="4">
+        <v>4234.0</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F53" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I53" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J53" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M53" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P53" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2">
+        <v>46225.88955635417</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C54" s="4">
+        <v>3286.0</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F54" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I54" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J54" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M54" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N54" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R54" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2">
+        <v>46225.89435642361</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C55" s="4">
+        <v>3652.0</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F55" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I55" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J55" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M55" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N55" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P55" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q55" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R55" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2">
+        <v>46227.11075491898</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" s="4">
+        <v>3824.0</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E56" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F56" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I56" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J56" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M56" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N56" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P56" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q56" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R56" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2">
+        <v>46227.113378634254</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C57" s="4">
+        <v>2911.0</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F57" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I57" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J57" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M57" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N57" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R57" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2">
+        <v>46227.11632569444</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C58" s="4">
+        <v>2062.0</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I58" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M58" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2">
+        <v>46227.12445994213</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59" s="4">
+        <v>3143.0</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F59" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I59" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J59" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M59" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N59" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R59" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2">
+        <v>46227.527796828705</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C60" s="4">
+        <v>4075.0</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F60" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I60" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J60" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M60" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N60" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R60" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2">
+        <v>46227.534867511575</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" s="4">
+        <v>66.0</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I61" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M61" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P61" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2">
+        <v>46227.544228506944</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" s="4">
+        <v>2544.0</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I62" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M62" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N62" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R62" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2">
+        <v>46227.54953957176</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C63" s="4">
+        <v>3881.0</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F63" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I63" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J63" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M63" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P63" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2">
+        <v>46227.558114363426</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C64" s="4">
+        <v>986.0</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E64" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F64" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I64" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J64" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M64" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="P64" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S64" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2">
+        <v>46227.561030937504</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C65" s="4">
+        <v>945.0</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E65" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F65" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I65" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J65" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M65" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P65" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R65" s="3">
         <v>4.0</v>
       </c>
     </row>
